--- a/static/templates/threat_template.xlsx
+++ b/static/templates/threat_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\grc_backend\static\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cydea\grc_backend\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6276DCA-E119-42D8-8D6F-556096AFF0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B407F0F-CE88-486A-BADD-D26253ACE65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="2196" windowWidth="20520" windowHeight="8880" xr2:uid="{2A3534EE-6672-4D27-A71A-32336A4265C6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A3534EE-6672-4D27-A71A-32336A4265C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -568,9 +568,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -630,9 +631,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -670,7 +671,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -776,7 +777,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -918,7 +919,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -931,7 +932,7 @@
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -944,7 +945,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -958,7 +959,7 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -972,7 +973,7 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -986,7 +987,7 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1000,7 +1001,7 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1014,7 +1015,7 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1028,7 +1029,7 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1042,7 +1043,7 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1056,7 +1057,7 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
